--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBCFF96-52CA-F745-A928-1642337C4464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0123B7-A1C1-604C-9C4D-EBCF745836E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="31420" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40380" yWindow="-7160" windowWidth="35300" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="yaml" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$M$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$Q$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="415">
   <si>
     <t>subsector</t>
   </si>
@@ -1304,16 +1304,31 @@
     <t>magnitude_description</t>
   </si>
   <si>
-    <t>strategy_NDC_3</t>
-  </si>
-  <si>
-    <t>strategy_NDC_3_Low_CCSQ</t>
-  </si>
-  <si>
-    <t>strategy_NDC_3_Hig_CCSQ</t>
-  </si>
-  <si>
-    <t>strategy_NDC_3_Hig_price</t>
+    <t>TX:ENFU:ADJ_EXPORTS</t>
+  </si>
+  <si>
+    <t>ENFU</t>
+  </si>
+  <si>
+    <t>Increase OR Decrease exports of fuels</t>
+  </si>
+  <si>
+    <t>transformation_enfu_adj_exports.yaml</t>
+  </si>
+  <si>
+    <t>strategy_1</t>
+  </si>
+  <si>
+    <t>strategy_2</t>
+  </si>
+  <si>
+    <t>strategy_3</t>
+  </si>
+  <si>
+    <t>strategy_4</t>
+  </si>
+  <si>
+    <t>strategy_5</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1593,6 +1608,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1898,7 +1914,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
@@ -1911,10 +1927,10 @@
     <col min="9" max="10" width="35" style="4" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.83203125" style="30" customWidth="1"/>
-    <col min="13" max="16" width="18.5" style="32" customWidth="1"/>
+    <col min="13" max="17" width="18.5" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
@@ -1952,19 +1968,22 @@
         <v>206</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+      <c r="Q1" s="35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>208</v>
       </c>
@@ -1993,20 +2012,13 @@
       <c r="L2" s="10">
         <v>12</v>
       </c>
-      <c r="M2" s="13">
-        <v>1</v>
-      </c>
-      <c r="N2" s="13">
-        <v>1</v>
-      </c>
-      <c r="O2" s="13">
-        <v>1</v>
-      </c>
-      <c r="P2" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>208</v>
       </c>
@@ -2039,8 +2051,9 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
-    </row>
-    <row r="4" spans="1:16" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>208</v>
       </c>
@@ -2069,20 +2082,13 @@
       <c r="L4" s="10">
         <v>12</v>
       </c>
-      <c r="M4" s="13">
-        <v>1</v>
-      </c>
-      <c r="N4" s="13">
-        <v>1</v>
-      </c>
-      <c r="O4" s="13">
-        <v>1</v>
-      </c>
-      <c r="P4" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>208</v>
       </c>
@@ -2111,20 +2117,13 @@
       <c r="L5" s="10">
         <v>12</v>
       </c>
-      <c r="M5" s="13">
-        <v>1</v>
-      </c>
-      <c r="N5" s="13">
-        <v>1</v>
-      </c>
-      <c r="O5" s="13">
-        <v>1</v>
-      </c>
-      <c r="P5" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+    </row>
+    <row r="6" spans="1:17" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>208</v>
       </c>
@@ -2161,8 +2160,9 @@
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q6" s="13"/>
+    </row>
+    <row r="7" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>222</v>
       </c>
@@ -2192,17 +2192,12 @@
         <v>12</v>
       </c>
       <c r="M7" s="13"/>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
-        <v>3</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" spans="1:17" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>222</v>
       </c>
@@ -2235,20 +2230,13 @@
       <c r="L8" s="10">
         <v>12</v>
       </c>
-      <c r="M8" s="13">
-        <v>1</v>
-      </c>
-      <c r="N8" s="13">
-        <v>1</v>
-      </c>
-      <c r="O8" s="13">
-        <v>1</v>
-      </c>
-      <c r="P8" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+    </row>
+    <row r="9" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>222</v>
       </c>
@@ -2285,8 +2273,9 @@
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
       <c r="P9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q9" s="13"/>
+    </row>
+    <row r="10" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>222</v>
       </c>
@@ -2317,20 +2306,17 @@
         <v>0.95</v>
       </c>
       <c r="L10" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13">
         <v>1</v>
       </c>
-      <c r="O10" s="13">
-        <v>1</v>
-      </c>
-      <c r="P10" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+    </row>
+    <row r="11" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>222</v>
       </c>
@@ -2359,20 +2345,13 @@
       <c r="L11" s="10">
         <v>12</v>
       </c>
-      <c r="M11" s="13">
-        <v>1</v>
-      </c>
-      <c r="N11" s="13">
-        <v>1</v>
-      </c>
-      <c r="O11" s="13">
-        <v>1</v>
-      </c>
-      <c r="P11" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+    </row>
+    <row r="12" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>222</v>
       </c>
@@ -2405,8 +2384,9 @@
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
       <c r="P12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q12" s="13"/>
+    </row>
+    <row r="13" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>222</v>
       </c>
@@ -2439,20 +2419,13 @@
       <c r="L13" s="10">
         <v>12</v>
       </c>
-      <c r="M13" s="13">
-        <v>1</v>
-      </c>
-      <c r="N13" s="13">
-        <v>1</v>
-      </c>
-      <c r="O13" s="13">
-        <v>1</v>
-      </c>
-      <c r="P13" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+    </row>
+    <row r="14" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>222</v>
       </c>
@@ -2485,20 +2458,13 @@
       <c r="L14" s="10">
         <v>12</v>
       </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="13">
-        <v>1</v>
-      </c>
-      <c r="O14" s="13">
-        <v>1</v>
-      </c>
-      <c r="P14" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+    </row>
+    <row r="15" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>222</v>
       </c>
@@ -2531,8 +2497,9 @@
       <c r="N15" s="13"/>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q15" s="13"/>
+    </row>
+    <row r="16" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
@@ -2569,14 +2536,11 @@
       <c r="N16" s="13">
         <v>1</v>
       </c>
-      <c r="O16" s="13">
-        <v>1</v>
-      </c>
-      <c r="P16" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+    </row>
+    <row r="17" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
@@ -2610,11 +2574,14 @@
         <v>12</v>
       </c>
       <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
+      <c r="N17" s="13">
+        <v>1</v>
+      </c>
       <c r="O17" s="13"/>
       <c r="P17" s="13"/>
-    </row>
-    <row r="18" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q17" s="13"/>
+    </row>
+    <row r="18" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>51</v>
       </c>
@@ -2647,20 +2614,13 @@
       <c r="L18" s="10">
         <v>12</v>
       </c>
-      <c r="M18" s="13">
-        <v>1</v>
-      </c>
-      <c r="N18" s="13">
-        <v>1</v>
-      </c>
-      <c r="O18" s="13">
-        <v>1</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+    </row>
+    <row r="19" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>51</v>
       </c>
@@ -2690,17 +2650,12 @@
         <v>12</v>
       </c>
       <c r="M19" s="13"/>
-      <c r="N19" s="13">
-        <v>1</v>
-      </c>
-      <c r="O19" s="13">
-        <v>1</v>
-      </c>
-      <c r="P19" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+    </row>
+    <row r="20" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>51</v>
       </c>
@@ -2730,17 +2685,12 @@
         <v>12</v>
       </c>
       <c r="M20" s="13"/>
-      <c r="N20" s="13">
-        <v>1</v>
-      </c>
-      <c r="O20" s="13">
-        <v>1</v>
-      </c>
-      <c r="P20" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+    </row>
+    <row r="21" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
@@ -2769,20 +2719,13 @@
       <c r="L21" s="10">
         <v>12</v>
       </c>
-      <c r="M21" s="13">
-        <v>1</v>
-      </c>
-      <c r="N21" s="13">
-        <v>1</v>
-      </c>
-      <c r="O21" s="13">
-        <v>1</v>
-      </c>
-      <c r="P21" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+    </row>
+    <row r="22" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>208</v>
       </c>
@@ -2815,20 +2758,13 @@
       <c r="L22" s="10">
         <v>12</v>
       </c>
-      <c r="M22" s="13">
-        <v>1</v>
-      </c>
-      <c r="N22" s="13">
-        <v>1</v>
-      </c>
-      <c r="O22" s="13">
-        <v>1</v>
-      </c>
-      <c r="P22" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+    </row>
+    <row r="23" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>208</v>
       </c>
@@ -2865,8 +2801,9 @@
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
       <c r="P23" s="13"/>
-    </row>
-    <row r="24" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q23" s="13"/>
+    </row>
+    <row r="24" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>208</v>
       </c>
@@ -2899,20 +2836,13 @@
       <c r="L24" s="10">
         <v>12</v>
       </c>
-      <c r="M24" s="13">
-        <v>1</v>
-      </c>
-      <c r="N24" s="13">
-        <v>1</v>
-      </c>
-      <c r="O24" s="13">
-        <v>1</v>
-      </c>
-      <c r="P24" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+    </row>
+    <row r="25" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>208</v>
       </c>
@@ -2949,8 +2879,9 @@
       <c r="N25" s="13"/>
       <c r="O25" s="13"/>
       <c r="P25" s="13"/>
-    </row>
-    <row r="26" spans="1:16" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q25" s="13"/>
+    </row>
+    <row r="26" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>208</v>
       </c>
@@ -2983,8 +2914,9 @@
       <c r="N26" s="13"/>
       <c r="O26" s="13"/>
       <c r="P26" s="13"/>
-    </row>
-    <row r="27" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q26" s="13"/>
+    </row>
+    <row r="27" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>208</v>
       </c>
@@ -3017,8 +2949,9 @@
       <c r="N27" s="13"/>
       <c r="O27" s="13"/>
       <c r="P27" s="13"/>
-    </row>
-    <row r="28" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q27" s="13"/>
+    </row>
+    <row r="28" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>208</v>
       </c>
@@ -3051,8 +2984,9 @@
       <c r="N28" s="13"/>
       <c r="O28" s="13"/>
       <c r="P28" s="13"/>
-    </row>
-    <row r="29" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q28" s="13"/>
+    </row>
+    <row r="29" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>208</v>
       </c>
@@ -3085,8 +3019,9 @@
       <c r="N29" s="13"/>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
-    </row>
-    <row r="30" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q29" s="13"/>
+    </row>
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>208</v>
       </c>
@@ -3119,8 +3054,9 @@
       <c r="N30" s="13"/>
       <c r="O30" s="13"/>
       <c r="P30" s="13"/>
-    </row>
-    <row r="31" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q30" s="13"/>
+    </row>
+    <row r="31" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>208</v>
       </c>
@@ -3153,8 +3089,9 @@
       <c r="N31" s="13"/>
       <c r="O31" s="13"/>
       <c r="P31" s="13"/>
-    </row>
-    <row r="32" spans="1:16" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q31" s="13"/>
+    </row>
+    <row r="32" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>208</v>
       </c>
@@ -3191,8 +3128,9 @@
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
-    </row>
-    <row r="33" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q32" s="13"/>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>305</v>
       </c>
@@ -3225,8 +3163,9 @@
       <c r="N33" s="13"/>
       <c r="O33" s="13"/>
       <c r="P33" s="13"/>
-    </row>
-    <row r="34" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q33" s="13"/>
+    </row>
+    <row r="34" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>305</v>
       </c>
@@ -3259,8 +3198,9 @@
       <c r="N34" s="13"/>
       <c r="O34" s="13"/>
       <c r="P34" s="13"/>
-    </row>
-    <row r="35" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q34" s="13"/>
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>222</v>
       </c>
@@ -3293,8 +3233,9 @@
       <c r="N35" s="13"/>
       <c r="O35" s="13"/>
       <c r="P35" s="13"/>
-    </row>
-    <row r="36" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q35" s="13"/>
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>222</v>
       </c>
@@ -3323,20 +3264,13 @@
       <c r="L36" s="10">
         <v>12</v>
       </c>
-      <c r="M36" s="13">
-        <v>1</v>
-      </c>
-      <c r="N36" s="13">
-        <v>1</v>
-      </c>
-      <c r="O36" s="13">
-        <v>1</v>
-      </c>
-      <c r="P36" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>222</v>
       </c>
@@ -3369,8 +3303,9 @@
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
-    </row>
-    <row r="38" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q37" s="13"/>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
         <v>208</v>
       </c>
@@ -3403,8 +3338,9 @@
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
-    </row>
-    <row r="39" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q38" s="13"/>
+    </row>
+    <row r="39" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>208</v>
       </c>
@@ -3437,8 +3373,9 @@
       <c r="N39" s="13"/>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
-    </row>
-    <row r="40" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q39" s="13"/>
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>222</v>
       </c>
@@ -3472,19 +3409,16 @@
         <v>12</v>
       </c>
       <c r="M40" s="13">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="N40" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="O40" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="P40" s="13">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="O40" s="13"/>
+      <c r="P40" s="13"/>
+      <c r="Q40" s="13"/>
+    </row>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>222</v>
       </c>
@@ -3515,22 +3449,19 @@
         <v>0.25</v>
       </c>
       <c r="L41" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M41" s="13">
         <v>1</v>
       </c>
       <c r="N41" s="13">
-        <v>1</v>
-      </c>
-      <c r="O41" s="13">
-        <v>1</v>
-      </c>
-      <c r="P41" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="13"/>
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>222</v>
       </c>
@@ -3561,22 +3492,17 @@
         <v>0.25</v>
       </c>
       <c r="L42" s="10">
-        <v>10</v>
-      </c>
-      <c r="M42" s="13">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M42" s="13"/>
       <c r="N42" s="13">
-        <v>1</v>
-      </c>
-      <c r="O42" s="13">
-        <v>1</v>
-      </c>
-      <c r="P42" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="O42" s="13"/>
+      <c r="P42" s="13"/>
+      <c r="Q42" s="13"/>
+    </row>
+    <row r="43" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>222</v>
       </c>
@@ -3603,22 +3529,17 @@
         <v>0.25</v>
       </c>
       <c r="L43" s="10">
-        <v>10</v>
-      </c>
-      <c r="M43" s="13">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M43" s="13"/>
       <c r="N43" s="13">
         <v>1</v>
       </c>
-      <c r="O43" s="13">
-        <v>1</v>
-      </c>
-      <c r="P43" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>222</v>
       </c>
@@ -3645,22 +3566,15 @@
         <v>0.7</v>
       </c>
       <c r="L44" s="10">
-        <v>10</v>
-      </c>
-      <c r="M44" s="13">
-        <v>1</v>
-      </c>
-      <c r="N44" s="13">
-        <v>1</v>
-      </c>
-      <c r="O44" s="13">
-        <v>1</v>
-      </c>
-      <c r="P44" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>222</v>
       </c>
@@ -3691,22 +3605,17 @@
         <v>0.7</v>
       </c>
       <c r="L45" s="10">
-        <v>10</v>
-      </c>
-      <c r="M45" s="13">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M45" s="13"/>
       <c r="N45" s="13">
         <v>1</v>
       </c>
-      <c r="O45" s="13">
-        <v>1</v>
-      </c>
-      <c r="P45" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13"/>
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>222</v>
       </c>
@@ -3737,22 +3646,15 @@
         <v>0.7</v>
       </c>
       <c r="L46" s="10">
-        <v>10</v>
-      </c>
-      <c r="M46" s="13">
-        <v>1</v>
-      </c>
-      <c r="N46" s="13">
-        <v>1</v>
-      </c>
-      <c r="O46" s="13">
-        <v>1</v>
-      </c>
-      <c r="P46" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="13"/>
+      <c r="Q46" s="13"/>
+    </row>
+    <row r="47" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>222</v>
       </c>
@@ -3779,22 +3681,15 @@
         <v>0.25</v>
       </c>
       <c r="L47" s="10">
-        <v>10</v>
-      </c>
-      <c r="M47" s="13">
-        <v>1</v>
-      </c>
-      <c r="N47" s="13">
-        <v>2</v>
-      </c>
-      <c r="O47" s="13">
-        <v>2</v>
-      </c>
-      <c r="P47" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+    </row>
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>222</v>
       </c>
@@ -3825,22 +3720,17 @@
         <v>0.2</v>
       </c>
       <c r="L48" s="10">
-        <v>10</v>
-      </c>
-      <c r="M48" s="13">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M48" s="13"/>
       <c r="N48" s="13">
         <v>1</v>
       </c>
-      <c r="O48" s="13">
-        <v>1</v>
-      </c>
-      <c r="P48" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+    </row>
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>222</v>
       </c>
@@ -3871,22 +3761,17 @@
         <v>0.3</v>
       </c>
       <c r="L49" s="10">
-        <v>10</v>
-      </c>
-      <c r="M49" s="13">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M49" s="13"/>
       <c r="N49" s="13">
         <v>1</v>
       </c>
-      <c r="O49" s="13">
-        <v>1</v>
-      </c>
-      <c r="P49" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+    </row>
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
         <v>222</v>
       </c>
@@ -3917,22 +3802,15 @@
         <v>358</v>
       </c>
       <c r="L50" s="10">
-        <v>10</v>
-      </c>
-      <c r="M50" s="13">
-        <v>1</v>
-      </c>
-      <c r="N50" s="13">
-        <v>1</v>
-      </c>
-      <c r="O50" s="13">
-        <v>1</v>
-      </c>
-      <c r="P50" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+    </row>
+    <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
@@ -3965,8 +3843,9 @@
       <c r="N51" s="13"/>
       <c r="O51" s="13"/>
       <c r="P51" s="13"/>
-    </row>
-    <row r="52" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q51" s="13"/>
+    </row>
+    <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
@@ -4003,8 +3882,9 @@
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
-    </row>
-    <row r="53" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q52" s="13"/>
+    </row>
+    <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>365</v>
       </c>
@@ -4037,20 +3917,13 @@
       <c r="L53" s="10">
         <v>12</v>
       </c>
-      <c r="M53" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N53" s="13">
-        <v>1</v>
-      </c>
-      <c r="O53" s="13">
-        <v>1</v>
-      </c>
-      <c r="P53" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+    </row>
+    <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>365</v>
       </c>
@@ -4087,8 +3960,9 @@
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
       <c r="P54" s="13"/>
-    </row>
-    <row r="55" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q54" s="13"/>
+    </row>
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
         <v>365</v>
       </c>
@@ -4125,8 +3999,9 @@
       <c r="N55" s="13"/>
       <c r="O55" s="13"/>
       <c r="P55" s="13"/>
-    </row>
-    <row r="56" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q55" s="13"/>
+    </row>
+    <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
         <v>365</v>
       </c>
@@ -4159,20 +4034,13 @@
       <c r="L56" s="10">
         <v>12</v>
       </c>
-      <c r="M56" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N56" s="13">
-        <v>1</v>
-      </c>
-      <c r="O56" s="13">
-        <v>1</v>
-      </c>
-      <c r="P56" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+    </row>
+    <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
         <v>365</v>
       </c>
@@ -4201,20 +4069,13 @@
       <c r="L57" s="10">
         <v>12</v>
       </c>
-      <c r="M57" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N57" s="13">
-        <v>1</v>
-      </c>
-      <c r="O57" s="13">
-        <v>1</v>
-      </c>
-      <c r="P57" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+    </row>
+    <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
         <v>365</v>
       </c>
@@ -4247,20 +4108,13 @@
       <c r="L58" s="10">
         <v>12</v>
       </c>
-      <c r="M58" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N58" s="13">
-        <v>1</v>
-      </c>
-      <c r="O58" s="13">
-        <v>1</v>
-      </c>
-      <c r="P58" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="13"/>
+      <c r="Q58" s="13"/>
+    </row>
+    <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
         <v>365</v>
       </c>
@@ -4293,8 +4147,9 @@
       <c r="N59" s="13"/>
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
-    </row>
-    <row r="60" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q59" s="13"/>
+    </row>
+    <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
         <v>365</v>
       </c>
@@ -4323,20 +4178,13 @@
       <c r="L60" s="10">
         <v>12</v>
       </c>
-      <c r="M60" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N60" s="13">
-        <v>1</v>
-      </c>
-      <c r="O60" s="13">
-        <v>1</v>
-      </c>
-      <c r="P60" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
+      <c r="Q60" s="13"/>
+    </row>
+    <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
         <v>365</v>
       </c>
@@ -4373,8 +4221,9 @@
       <c r="N61" s="13"/>
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
-    </row>
-    <row r="62" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q61" s="13"/>
+    </row>
+    <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
         <v>365</v>
       </c>
@@ -4407,38 +4256,57 @@
       <c r="L62" s="10">
         <v>12</v>
       </c>
-      <c r="M62" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N62" s="13">
-        <v>1</v>
-      </c>
-      <c r="O62" s="13">
-        <v>1</v>
-      </c>
-      <c r="P62" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="16"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="25"/>
-      <c r="N63" s="25"/>
-      <c r="O63" s="25"/>
-      <c r="P63" s="25"/>
-    </row>
-    <row r="64" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+    </row>
+    <row r="63" spans="1:18" ht="68" x14ac:dyDescent="0.2">
+      <c r="A63" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="C63" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="D63" s="36"/>
+      <c r="E63" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="K63" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="L63" s="10">
+        <v>12</v>
+      </c>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13">
+        <v>4</v>
+      </c>
+      <c r="P63" s="13">
+        <v>5</v>
+      </c>
+      <c r="Q63" s="13">
+        <v>5</v>
+      </c>
+      <c r="R63" s="42"/>
+    </row>
+    <row r="64" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -4455,8 +4323,9 @@
       <c r="N64" s="25"/>
       <c r="O64" s="25"/>
       <c r="P64" s="25"/>
-    </row>
-    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q64" s="25"/>
+    </row>
+    <row r="65" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -4473,10 +4342,143 @@
       <c r="N65" s="25"/>
       <c r="O65" s="25"/>
       <c r="P65" s="25"/>
+      <c r="Q65" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M62" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="M1:M45 M47:M1048576">
+  <autoFilter ref="A1:Q63" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M13">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M15">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M46">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M64:M1048576 M1:M7 M63:Q63 M47:M62 O56:Q62 O47:Q50 O40:Q45 O4:Q5 O53:Q53 O36:Q36 O24:Q24 O19:Q22 O16:Q17 O10:Q14 O7:Q8 M9:M12 M14 M16:M45">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N39 N51:N62">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N40">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N64:N1048576">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O64:O1048576 O18 O37:O39 O2:O3 O54:O55 O52 O15 O9 O23 O25:O35 O6">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O46:Q46">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -4488,43 +4490,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N17:N18 N21:N35 N15 N12 N37:N40 N1:N7 N9 N46:P47 N45 N47:N1048576">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41:P44 N16:P16 N19:P20 N36:P36 N8:P8 N13:P14 N10:P11 N48:P49">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O17:O18 O21:O35 O63:O1048576 O61 O59 O15 O12 O37:O39 O2:O7 O9 O54:O55 O48:O52 O45">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O53">
+  <conditionalFormatting sqref="O51:Q51">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -4536,79 +4502,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O56:O58">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O60">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O62">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O1:P1">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P17:P18 P21:P35 P63:P1048576 P61 P59 P15 P12 P37:P39 P2:P7 P9 P54:P55 P48:P52 P45">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P53">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P56:P58">
+  <conditionalFormatting sqref="P1:Q1">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -4620,8 +4514,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P60">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="P64:Q1048576 P18:Q18 P15:Q15 P37:Q39 P2:Q3 P9:Q9 P54:Q55 P52:Q52 P23:Q23 P25:Q35 P6:Q6">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4632,67 +4526,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P62">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O40">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P40">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N50:P50">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N45:P45">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M46">
+  <conditionalFormatting sqref="N41:N50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4713,7 +4547,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -5590,6 +5424,20 @@
         <v>202</v>
       </c>
     </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0123B7-A1C1-604C-9C4D-EBCF745836E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692A54B-84A8-144C-AC4C-7B8056F7347B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40380" yWindow="-7160" windowWidth="35300" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2010,10 +2010,12 @@
         <v>0.45</v>
       </c>
       <c r="L2" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
+      <c r="N2" s="13">
+        <v>3</v>
+      </c>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
       <c r="Q2" s="13"/>
@@ -2045,10 +2047,12 @@
         <v>0.5</v>
       </c>
       <c r="L3" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="N3" s="13">
+        <v>3</v>
+      </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
@@ -2080,10 +2084,12 @@
         <v>0.3</v>
       </c>
       <c r="L4" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="N4" s="13">
+        <v>3</v>
+      </c>
       <c r="O4" s="13"/>
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
@@ -2115,10 +2121,12 @@
         <v>217</v>
       </c>
       <c r="L5" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
+      <c r="N5" s="13">
+        <v>1</v>
+      </c>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
@@ -2154,7 +2162,7 @@
         <v>0.2</v>
       </c>
       <c r="L6" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
@@ -2189,7 +2197,7 @@
         <v>50</v>
       </c>
       <c r="L7" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
@@ -2228,7 +2236,7 @@
         <v>229</v>
       </c>
       <c r="L8" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
@@ -2267,7 +2275,7 @@
         <v>0.95</v>
       </c>
       <c r="L9" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -2306,11 +2314,11 @@
         <v>0.95</v>
       </c>
       <c r="L10" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13"/>
@@ -2343,7 +2351,7 @@
         <v>0.8</v>
       </c>
       <c r="L11" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
@@ -2378,7 +2386,7 @@
         <v>0.8</v>
       </c>
       <c r="L12" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
@@ -2417,7 +2425,7 @@
         <v>0.3</v>
       </c>
       <c r="L13" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
@@ -2456,7 +2464,7 @@
         <v>0.4</v>
       </c>
       <c r="L14" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
@@ -2491,10 +2499,12 @@
         <v>252</v>
       </c>
       <c r="L15" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="N15" s="13">
+        <v>1</v>
+      </c>
       <c r="O15" s="13"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -2530,7 +2540,7 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13">
@@ -2571,7 +2581,7 @@
         <v>0.3</v>
       </c>
       <c r="L17" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M17" s="13"/>
       <c r="N17" s="13">
@@ -2612,10 +2622,12 @@
         <v>0.1</v>
       </c>
       <c r="L18" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="N18" s="13">
+        <v>1</v>
+      </c>
       <c r="O18" s="13"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -2647,10 +2659,12 @@
         <v>0.1</v>
       </c>
       <c r="L19" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
+      <c r="N19" s="13">
+        <v>1</v>
+      </c>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -2682,10 +2696,12 @@
         <v>0.1</v>
       </c>
       <c r="L20" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
+      <c r="N20" s="13">
+        <v>1</v>
+      </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -2717,10 +2733,12 @@
         <v>0.1</v>
       </c>
       <c r="L21" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
+      <c r="N21" s="13">
+        <v>1</v>
+      </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -2756,7 +2774,7 @@
         <v>0.999</v>
       </c>
       <c r="L22" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13"/>
@@ -2795,7 +2813,7 @@
         <v>0.95</v>
       </c>
       <c r="L23" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
@@ -2834,7 +2852,7 @@
         <v>0.2</v>
       </c>
       <c r="L24" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
@@ -2873,7 +2891,7 @@
         <v>0.1</v>
       </c>
       <c r="L25" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="13"/>
@@ -2908,7 +2926,7 @@
         <v>0.9</v>
       </c>
       <c r="L26" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="13"/>
@@ -2943,7 +2961,7 @@
         <v>291</v>
       </c>
       <c r="L27" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
@@ -2978,7 +2996,7 @@
         <v>293</v>
       </c>
       <c r="L28" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
@@ -3013,7 +3031,7 @@
         <v>295</v>
       </c>
       <c r="L29" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
@@ -3048,7 +3066,7 @@
         <v>298</v>
       </c>
       <c r="L30" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
@@ -3083,7 +3101,7 @@
         <v>0.5</v>
       </c>
       <c r="L31" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M31" s="13"/>
       <c r="N31" s="13"/>
@@ -3122,7 +3140,7 @@
         <v>0.3</v>
       </c>
       <c r="L32" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M32" s="13"/>
       <c r="N32" s="13"/>
@@ -3157,7 +3175,7 @@
         <v>0.5</v>
       </c>
       <c r="L33" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M33" s="13"/>
       <c r="N33" s="13"/>
@@ -3192,7 +3210,7 @@
         <v>0.9</v>
       </c>
       <c r="L34" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M34" s="13"/>
       <c r="N34" s="13"/>
@@ -3227,7 +3245,7 @@
         <v>0.5</v>
       </c>
       <c r="L35" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
@@ -3262,7 +3280,7 @@
         <v>0.5</v>
       </c>
       <c r="L36" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
@@ -3297,7 +3315,7 @@
         <v>0.95</v>
       </c>
       <c r="L37" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
@@ -3332,7 +3350,7 @@
         <v>0.2</v>
       </c>
       <c r="L38" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M38" s="13"/>
       <c r="N38" s="13"/>
@@ -3367,7 +3385,7 @@
         <v>0.2</v>
       </c>
       <c r="L39" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="13"/>
@@ -3406,10 +3424,10 @@
         <v>0.25</v>
       </c>
       <c r="L40" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M40" s="13">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N40" s="13">
         <v>2</v>
@@ -3449,13 +3467,13 @@
         <v>0.25</v>
       </c>
       <c r="L41" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M41" s="13">
         <v>1</v>
       </c>
       <c r="N41" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="13"/>
       <c r="P41" s="13"/>
@@ -3492,12 +3510,10 @@
         <v>0.25</v>
       </c>
       <c r="L42" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M42" s="13"/>
-      <c r="N42" s="13">
-        <v>2</v>
-      </c>
+      <c r="N42" s="13"/>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
@@ -3529,7 +3545,7 @@
         <v>0.25</v>
       </c>
       <c r="L43" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="13">
@@ -3566,10 +3582,12 @@
         <v>0.7</v>
       </c>
       <c r="L44" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
+      <c r="N44" s="13">
+        <v>1</v>
+      </c>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
@@ -3605,7 +3623,7 @@
         <v>0.7</v>
       </c>
       <c r="L45" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="13">
@@ -3646,10 +3664,12 @@
         <v>0.7</v>
       </c>
       <c r="L46" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
+      <c r="N46" s="13">
+        <v>1</v>
+      </c>
       <c r="O46" s="13"/>
       <c r="P46" s="13"/>
       <c r="Q46" s="13"/>
@@ -3681,10 +3701,12 @@
         <v>0.25</v>
       </c>
       <c r="L47" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
+      <c r="N47" s="13">
+        <v>1</v>
+      </c>
       <c r="O47" s="13"/>
       <c r="P47" s="13"/>
       <c r="Q47" s="13"/>
@@ -3720,7 +3742,7 @@
         <v>0.2</v>
       </c>
       <c r="L48" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13">
@@ -3761,7 +3783,7 @@
         <v>0.3</v>
       </c>
       <c r="L49" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13">
@@ -3802,10 +3824,12 @@
         <v>358</v>
       </c>
       <c r="L50" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
+      <c r="N50" s="13">
+        <v>1</v>
+      </c>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
@@ -3837,7 +3861,7 @@
         <v>0.85</v>
       </c>
       <c r="L51" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
@@ -3876,7 +3900,7 @@
         <v>0.9</v>
       </c>
       <c r="L52" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
@@ -3915,10 +3939,12 @@
         <v>370</v>
       </c>
       <c r="L53" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
+      <c r="N53" s="13">
+        <v>1</v>
+      </c>
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
@@ -3954,7 +3980,7 @@
         <v>374</v>
       </c>
       <c r="L54" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
@@ -3993,7 +4019,7 @@
         <v>378</v>
       </c>
       <c r="L55" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
@@ -4032,10 +4058,12 @@
         <v>0.3</v>
       </c>
       <c r="L56" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
+      <c r="N56" s="13">
+        <v>1</v>
+      </c>
       <c r="O56" s="13"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
@@ -4067,10 +4095,12 @@
         <v>385</v>
       </c>
       <c r="L57" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
+      <c r="N57" s="13">
+        <v>1</v>
+      </c>
       <c r="O57" s="13"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
@@ -4106,7 +4136,7 @@
         <v>0.85</v>
       </c>
       <c r="L58" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M58" s="13"/>
       <c r="N58" s="13"/>
@@ -4141,7 +4171,7 @@
         <v>0.85</v>
       </c>
       <c r="L59" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
@@ -4176,10 +4206,12 @@
         <v>0.85</v>
       </c>
       <c r="L60" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
+      <c r="N60" s="13">
+        <v>1</v>
+      </c>
       <c r="O60" s="13"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
@@ -4215,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="L61" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
@@ -4254,10 +4286,12 @@
         <v>0.95</v>
       </c>
       <c r="L62" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
+      <c r="N62" s="13">
+        <v>1</v>
+      </c>
       <c r="O62" s="13"/>
       <c r="P62" s="13"/>
       <c r="Q62" s="13"/>
@@ -4291,7 +4325,7 @@
         <v>0.8</v>
       </c>
       <c r="L63" s="10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
@@ -4418,8 +4452,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N39 N51:N62">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="N40">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4430,8 +4464,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N40">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="N41:N50">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N51:N62 N2:N39">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4526,18 +4572,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N41:N50">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F692A54B-84A8-144C-AC4C-7B8056F7347B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA59A516-75A2-7846-97F9-9021808A3D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-44000" yWindow="-7160" windowWidth="34260" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2010,15 +2010,23 @@
         <v>0.45</v>
       </c>
       <c r="L2" s="10">
-        <v>7</v>
-      </c>
-      <c r="M2" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M2" s="13">
+        <v>1</v>
+      </c>
       <c r="N2" s="13">
-        <v>3</v>
-      </c>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="O2" s="13">
+        <v>1</v>
+      </c>
+      <c r="P2" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:17" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
@@ -2047,15 +2055,23 @@
         <v>0.5</v>
       </c>
       <c r="L3" s="10">
-        <v>7</v>
-      </c>
-      <c r="M3" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M3" s="13">
+        <v>1</v>
+      </c>
       <c r="N3" s="13">
-        <v>3</v>
-      </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="O3" s="13">
+        <v>1</v>
+      </c>
+      <c r="P3" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
@@ -2084,15 +2100,21 @@
         <v>0.3</v>
       </c>
       <c r="L4" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M4" s="13"/>
       <c r="N4" s="13">
-        <v>3</v>
-      </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="O4" s="13">
+        <v>1</v>
+      </c>
+      <c r="P4" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
@@ -2121,15 +2143,23 @@
         <v>217</v>
       </c>
       <c r="L5" s="10">
-        <v>7</v>
-      </c>
-      <c r="M5" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M5" s="13">
+        <v>1</v>
+      </c>
       <c r="N5" s="13">
         <v>1</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="O5" s="13">
+        <v>1</v>
+      </c>
+      <c r="P5" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
@@ -2162,13 +2192,21 @@
         <v>0.2</v>
       </c>
       <c r="L6" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
+      <c r="N6" s="13">
+        <v>1</v>
+      </c>
+      <c r="O6" s="13">
+        <v>1</v>
+      </c>
+      <c r="P6" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
@@ -2197,13 +2235,19 @@
         <v>50</v>
       </c>
       <c r="L7" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="O7" s="13">
+        <v>1</v>
+      </c>
+      <c r="P7" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
@@ -2236,13 +2280,23 @@
         <v>229</v>
       </c>
       <c r="L8" s="10">
-        <v>7</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="13">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13">
+        <v>1</v>
+      </c>
+      <c r="P8" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
@@ -2275,13 +2329,21 @@
         <v>0.95</v>
       </c>
       <c r="L9" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
+      <c r="N9" s="13">
+        <v>1</v>
+      </c>
+      <c r="O9" s="13">
+        <v>1</v>
+      </c>
+      <c r="P9" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
@@ -2314,15 +2376,21 @@
         <v>0.95</v>
       </c>
       <c r="L10" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="13">
+        <v>1</v>
+      </c>
+      <c r="P10" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
@@ -2351,13 +2419,21 @@
         <v>0.8</v>
       </c>
       <c r="L11" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="N11" s="13">
+        <v>1</v>
+      </c>
+      <c r="O11" s="13">
+        <v>1</v>
+      </c>
+      <c r="P11" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
@@ -2386,13 +2462,21 @@
         <v>0.8</v>
       </c>
       <c r="L12" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
+      <c r="N12" s="13">
+        <v>1</v>
+      </c>
+      <c r="O12" s="13">
+        <v>1</v>
+      </c>
+      <c r="P12" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
@@ -2421,17 +2505,25 @@
       <c r="J13" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="K13" s="17">
-        <v>0.3</v>
+      <c r="K13" s="15">
+        <v>0.8</v>
       </c>
       <c r="L13" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="N13" s="13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="13">
+        <v>1</v>
+      </c>
+      <c r="P13" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
@@ -2464,13 +2556,23 @@
         <v>0.4</v>
       </c>
       <c r="L14" s="10">
-        <v>7</v>
-      </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M14" s="13">
+        <v>1</v>
+      </c>
+      <c r="N14" s="13">
+        <v>1</v>
+      </c>
+      <c r="O14" s="13">
+        <v>1</v>
+      </c>
+      <c r="P14" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
@@ -2499,15 +2601,21 @@
         <v>252</v>
       </c>
       <c r="L15" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13">
         <v>1</v>
       </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="O15" s="13">
+        <v>1</v>
+      </c>
+      <c r="P15" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
@@ -2540,15 +2648,21 @@
         <v>0.5</v>
       </c>
       <c r="L16" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13">
         <v>1</v>
       </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
+      <c r="O16" s="13">
+        <v>1</v>
+      </c>
+      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
@@ -2581,15 +2695,23 @@
         <v>0.3</v>
       </c>
       <c r="L17" s="10">
-        <v>7</v>
-      </c>
-      <c r="M17" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M17" s="13">
+        <v>1</v>
+      </c>
       <c r="N17" s="13">
         <v>1</v>
       </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
+      <c r="O17" s="13">
+        <v>1</v>
+      </c>
+      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
@@ -2622,15 +2744,21 @@
         <v>0.1</v>
       </c>
       <c r="L18" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13">
         <v>1</v>
       </c>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
+      <c r="O18" s="13">
+        <v>1</v>
+      </c>
+      <c r="P18" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
@@ -2659,15 +2787,23 @@
         <v>0.1</v>
       </c>
       <c r="L19" s="10">
-        <v>7</v>
-      </c>
-      <c r="M19" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M19" s="13">
+        <v>1</v>
+      </c>
       <c r="N19" s="13">
         <v>1</v>
       </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="O19" s="13">
+        <v>1</v>
+      </c>
+      <c r="P19" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
@@ -2696,15 +2832,21 @@
         <v>0.1</v>
       </c>
       <c r="L20" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M20" s="13"/>
       <c r="N20" s="13">
         <v>1</v>
       </c>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
+      <c r="O20" s="13">
+        <v>1</v>
+      </c>
+      <c r="P20" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
@@ -2733,15 +2875,21 @@
         <v>0.1</v>
       </c>
       <c r="L21" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13">
         <v>1</v>
       </c>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
+      <c r="O21" s="13">
+        <v>1</v>
+      </c>
+      <c r="P21" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
@@ -2774,13 +2922,23 @@
         <v>0.999</v>
       </c>
       <c r="L22" s="10">
-        <v>7</v>
-      </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M22" s="13">
+        <v>1</v>
+      </c>
+      <c r="N22" s="13">
+        <v>1</v>
+      </c>
+      <c r="O22" s="13">
+        <v>1</v>
+      </c>
+      <c r="P22" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
@@ -2813,13 +2971,21 @@
         <v>0.95</v>
       </c>
       <c r="L23" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
+      <c r="N23" s="13">
+        <v>1</v>
+      </c>
+      <c r="O23" s="13">
+        <v>1</v>
+      </c>
+      <c r="P23" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
@@ -2852,13 +3018,21 @@
         <v>0.2</v>
       </c>
       <c r="L24" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
+      <c r="N24" s="13">
+        <v>1</v>
+      </c>
+      <c r="O24" s="13">
+        <v>1</v>
+      </c>
+      <c r="P24" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
@@ -2891,13 +3065,21 @@
         <v>0.1</v>
       </c>
       <c r="L25" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
+      <c r="N25" s="13">
+        <v>1</v>
+      </c>
+      <c r="O25" s="13">
+        <v>1</v>
+      </c>
+      <c r="P25" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
@@ -2926,13 +3108,21 @@
         <v>0.9</v>
       </c>
       <c r="L26" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
+      <c r="N26" s="13">
+        <v>1</v>
+      </c>
+      <c r="O26" s="13">
+        <v>1</v>
+      </c>
+      <c r="P26" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
@@ -2961,13 +3151,21 @@
         <v>291</v>
       </c>
       <c r="L27" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
+      <c r="N27" s="13">
+        <v>1</v>
+      </c>
+      <c r="O27" s="13">
+        <v>1</v>
+      </c>
+      <c r="P27" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
@@ -2996,13 +3194,21 @@
         <v>293</v>
       </c>
       <c r="L28" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
+      <c r="N28" s="13">
+        <v>1</v>
+      </c>
+      <c r="O28" s="13">
+        <v>1</v>
+      </c>
+      <c r="P28" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
@@ -3031,13 +3237,21 @@
         <v>295</v>
       </c>
       <c r="L29" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
+      <c r="N29" s="13">
+        <v>1</v>
+      </c>
+      <c r="O29" s="13">
+        <v>1</v>
+      </c>
+      <c r="P29" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
@@ -3066,13 +3280,21 @@
         <v>298</v>
       </c>
       <c r="L30" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="13"/>
-      <c r="Q30" s="13"/>
+      <c r="N30" s="13">
+        <v>1</v>
+      </c>
+      <c r="O30" s="13">
+        <v>1</v>
+      </c>
+      <c r="P30" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
@@ -3101,13 +3323,23 @@
         <v>0.5</v>
       </c>
       <c r="L31" s="10">
-        <v>7</v>
-      </c>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M31" s="13">
+        <v>1</v>
+      </c>
+      <c r="N31" s="13">
+        <v>2</v>
+      </c>
+      <c r="O31" s="13">
+        <v>2</v>
+      </c>
+      <c r="P31" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>2</v>
+      </c>
     </row>
     <row r="32" spans="1:17" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
@@ -3140,13 +3372,21 @@
         <v>0.3</v>
       </c>
       <c r="L32" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="13"/>
-      <c r="Q32" s="13"/>
+      <c r="N32" s="13">
+        <v>1</v>
+      </c>
+      <c r="O32" s="13">
+        <v>1</v>
+      </c>
+      <c r="P32" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
@@ -3175,13 +3415,21 @@
         <v>0.5</v>
       </c>
       <c r="L33" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
+      <c r="N33" s="13">
+        <v>1</v>
+      </c>
+      <c r="O33" s="13">
+        <v>1</v>
+      </c>
+      <c r="P33" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
@@ -3210,13 +3458,21 @@
         <v>0.9</v>
       </c>
       <c r="L34" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="13"/>
+      <c r="N34" s="13">
+        <v>1</v>
+      </c>
+      <c r="O34" s="13">
+        <v>1</v>
+      </c>
+      <c r="P34" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
@@ -3245,13 +3501,21 @@
         <v>0.5</v>
       </c>
       <c r="L35" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
+      <c r="N35" s="13">
+        <v>1</v>
+      </c>
+      <c r="O35" s="13">
+        <v>1</v>
+      </c>
+      <c r="P35" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
@@ -3280,13 +3544,21 @@
         <v>0.5</v>
       </c>
       <c r="L36" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="13">
+        <v>1</v>
+      </c>
+      <c r="P36" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
@@ -3315,13 +3587,21 @@
         <v>0.95</v>
       </c>
       <c r="L37" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
+      <c r="N37" s="13">
+        <v>1</v>
+      </c>
+      <c r="O37" s="13">
+        <v>1</v>
+      </c>
+      <c r="P37" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
@@ -3350,13 +3630,21 @@
         <v>0.2</v>
       </c>
       <c r="L38" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
+      <c r="N38" s="13">
+        <v>2</v>
+      </c>
+      <c r="O38" s="13">
+        <v>2</v>
+      </c>
+      <c r="P38" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="13">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
@@ -3385,13 +3673,21 @@
         <v>0.2</v>
       </c>
       <c r="L39" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
+      <c r="N39" s="13">
+        <v>2</v>
+      </c>
+      <c r="O39" s="13">
+        <v>2</v>
+      </c>
+      <c r="P39" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="13">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
@@ -3424,17 +3720,23 @@
         <v>0.25</v>
       </c>
       <c r="L40" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M40" s="13">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="13">
-        <v>2</v>
-      </c>
-      <c r="O40" s="13"/>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="O40" s="13">
+        <v>3</v>
+      </c>
+      <c r="P40" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
@@ -3467,17 +3769,21 @@
         <v>0.25</v>
       </c>
       <c r="L41" s="10">
-        <v>7</v>
-      </c>
-      <c r="M41" s="13">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M41" s="13"/>
       <c r="N41" s="13">
         <v>1</v>
       </c>
-      <c r="O41" s="13"/>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13"/>
+      <c r="O41" s="13">
+        <v>1</v>
+      </c>
+      <c r="P41" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
@@ -3510,13 +3816,21 @@
         <v>0.25</v>
       </c>
       <c r="L42" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="13"/>
+      <c r="N42" s="13">
+        <v>1</v>
+      </c>
+      <c r="O42" s="13">
+        <v>1</v>
+      </c>
+      <c r="P42" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
@@ -3545,15 +3859,21 @@
         <v>0.25</v>
       </c>
       <c r="L43" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="13">
         <v>1</v>
       </c>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="O43" s="13">
+        <v>1</v>
+      </c>
+      <c r="P43" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
@@ -3582,15 +3902,21 @@
         <v>0.7</v>
       </c>
       <c r="L44" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="13">
         <v>1</v>
       </c>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
+      <c r="O44" s="13">
+        <v>1</v>
+      </c>
+      <c r="P44" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
@@ -3623,15 +3949,21 @@
         <v>0.7</v>
       </c>
       <c r="L45" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="13">
         <v>1</v>
       </c>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
+      <c r="O45" s="13">
+        <v>1</v>
+      </c>
+      <c r="P45" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
@@ -3664,15 +3996,21 @@
         <v>0.7</v>
       </c>
       <c r="L46" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="13">
         <v>1</v>
       </c>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="13"/>
+      <c r="O46" s="13">
+        <v>1</v>
+      </c>
+      <c r="P46" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
@@ -3701,15 +4039,23 @@
         <v>0.25</v>
       </c>
       <c r="L47" s="10">
-        <v>7</v>
-      </c>
-      <c r="M47" s="13"/>
+        <v>10</v>
+      </c>
+      <c r="M47" s="13">
+        <v>1</v>
+      </c>
       <c r="N47" s="13">
         <v>1</v>
       </c>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
+      <c r="O47" s="13">
+        <v>1</v>
+      </c>
+      <c r="P47" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
@@ -3742,15 +4088,21 @@
         <v>0.2</v>
       </c>
       <c r="L48" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13">
         <v>1</v>
       </c>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
+      <c r="O48" s="13">
+        <v>1</v>
+      </c>
+      <c r="P48" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
@@ -3783,15 +4135,21 @@
         <v>0.3</v>
       </c>
       <c r="L49" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13">
         <v>1</v>
       </c>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
+      <c r="O49" s="13">
+        <v>1</v>
+      </c>
+      <c r="P49" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
@@ -3824,15 +4182,21 @@
         <v>358</v>
       </c>
       <c r="L50" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13">
         <v>1</v>
       </c>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
+      <c r="O50" s="13">
+        <v>1</v>
+      </c>
+      <c r="P50" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
@@ -3861,13 +4225,21 @@
         <v>0.85</v>
       </c>
       <c r="L51" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
+      <c r="N51" s="13">
+        <v>1</v>
+      </c>
+      <c r="O51" s="13">
+        <v>1</v>
+      </c>
+      <c r="P51" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
@@ -3900,13 +4272,21 @@
         <v>0.9</v>
       </c>
       <c r="L52" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="13"/>
+      <c r="N52" s="13">
+        <v>1</v>
+      </c>
+      <c r="O52" s="13">
+        <v>1</v>
+      </c>
+      <c r="P52" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
@@ -3939,15 +4319,21 @@
         <v>370</v>
       </c>
       <c r="L53" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M53" s="13"/>
       <c r="N53" s="13">
         <v>1</v>
       </c>
-      <c r="O53" s="13"/>
-      <c r="P53" s="13"/>
-      <c r="Q53" s="13"/>
+      <c r="O53" s="13">
+        <v>1</v>
+      </c>
+      <c r="P53" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
@@ -3980,13 +4366,21 @@
         <v>374</v>
       </c>
       <c r="L54" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
-      <c r="Q54" s="13"/>
+      <c r="N54" s="13">
+        <v>1</v>
+      </c>
+      <c r="O54" s="13">
+        <v>1</v>
+      </c>
+      <c r="P54" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
@@ -4019,13 +4413,21 @@
         <v>378</v>
       </c>
       <c r="L55" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="13"/>
-      <c r="Q55" s="13"/>
+      <c r="N55" s="13">
+        <v>1</v>
+      </c>
+      <c r="O55" s="13">
+        <v>1</v>
+      </c>
+      <c r="P55" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
@@ -4058,15 +4460,21 @@
         <v>0.3</v>
       </c>
       <c r="L56" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M56" s="13"/>
       <c r="N56" s="13">
         <v>1</v>
       </c>
-      <c r="O56" s="13"/>
-      <c r="P56" s="13"/>
-      <c r="Q56" s="13"/>
+      <c r="O56" s="13">
+        <v>1</v>
+      </c>
+      <c r="P56" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9" t="s">
@@ -4095,15 +4503,21 @@
         <v>385</v>
       </c>
       <c r="L57" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M57" s="13"/>
       <c r="N57" s="13">
         <v>1</v>
       </c>
-      <c r="O57" s="13"/>
-      <c r="P57" s="13"/>
-      <c r="Q57" s="13"/>
+      <c r="O57" s="13">
+        <v>1</v>
+      </c>
+      <c r="P57" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
@@ -4136,13 +4550,21 @@
         <v>0.85</v>
       </c>
       <c r="L58" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13"/>
-      <c r="Q58" s="13"/>
+      <c r="N58" s="13">
+        <v>1</v>
+      </c>
+      <c r="O58" s="13">
+        <v>1</v>
+      </c>
+      <c r="P58" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
@@ -4171,13 +4593,21 @@
         <v>0.85</v>
       </c>
       <c r="L59" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
-      <c r="Q59" s="13"/>
+      <c r="N59" s="13">
+        <v>1</v>
+      </c>
+      <c r="O59" s="13">
+        <v>1</v>
+      </c>
+      <c r="P59" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
@@ -4206,15 +4636,21 @@
         <v>0.85</v>
       </c>
       <c r="L60" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M60" s="13"/>
       <c r="N60" s="13">
         <v>1</v>
       </c>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
-      <c r="Q60" s="13"/>
+      <c r="O60" s="13">
+        <v>1</v>
+      </c>
+      <c r="P60" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
@@ -4247,13 +4683,21 @@
         <v>1</v>
       </c>
       <c r="L61" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13"/>
-      <c r="Q61" s="13"/>
+      <c r="N61" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="O61" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="P61" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="Q61" s="13">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="62" spans="1:18" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
@@ -4286,15 +4730,21 @@
         <v>0.95</v>
       </c>
       <c r="L62" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M62" s="13"/>
       <c r="N62" s="13">
         <v>1</v>
       </c>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
+      <c r="O62" s="13">
+        <v>1</v>
+      </c>
+      <c r="P62" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
@@ -4325,18 +4775,18 @@
         <v>0.8</v>
       </c>
       <c r="L63" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
       <c r="O63" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P63" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R63" s="42"/>
     </row>
@@ -4381,7 +4831,7 @@
   </sheetData>
   <autoFilter ref="A1:Q63" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4393,7 +4843,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4405,7 +4855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4417,18 +4867,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64:M1048576 M1:M7 M63:Q63 M47:M62 O56:Q62 O47:Q50 O40:Q45 O4:Q5 O53:Q53 O36:Q36 O24:Q24 O19:Q22 O16:Q17 O10:Q14 O7:Q8 M9:M12 M14 M16:M45">
     <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
@@ -4440,44 +4878,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N40">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N41:N50">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N51:N62 N2:N39">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="M64:M1048576 M1:M7 M47:M62 M9:M12 M14 M63:Q63 M16:M45">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4489,7 +4891,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N64:N1048576">
-    <cfRule type="colorScale" priority="41">
+    <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4500,8 +4902,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="N1:P1">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4512,8 +4914,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O64:O1048576 O18 O37:O39 O2:O3 O54:O55 O52 O15 O9 O23 O25:O35 O6">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="N8:Q62 N7 N2:Q6">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4524,8 +4926,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O46:Q46">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="O64:O1048576">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4536,8 +4938,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O51:Q51">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="P64:P1048576">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4548,8 +4950,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P1:Q1">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4560,8 +4962,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P64:Q1048576 P18:Q18 P15:Q15 P37:Q39 P2:Q3 P9:Q9 P54:Q55 P52:Q52 P23:Q23 P25:Q35 P6:Q6">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="Q64:Q1048576">
+    <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA59A516-75A2-7846-97F9-9021808A3D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5D48F-C4A0-0147-ACFE-2E88B31A7036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-44000" yWindow="-7160" windowWidth="34260" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2240,10 +2240,10 @@
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P7" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="13">
         <v>1</v>
@@ -2924,9 +2924,7 @@
       <c r="L22" s="10">
         <v>10</v>
       </c>
-      <c r="M22" s="13">
-        <v>1</v>
-      </c>
+      <c r="M22" s="13"/>
       <c r="N22" s="13">
         <v>1</v>
       </c>
@@ -3110,12 +3108,14 @@
       <c r="L26" s="10">
         <v>10</v>
       </c>
-      <c r="M26" s="13"/>
+      <c r="M26" s="13">
+        <v>1</v>
+      </c>
       <c r="N26" s="13">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="O26" s="13">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="P26" s="13">
         <v>1</v>
@@ -3153,7 +3153,9 @@
       <c r="L27" s="10">
         <v>10</v>
       </c>
-      <c r="M27" s="13"/>
+      <c r="M27" s="13">
+        <v>1</v>
+      </c>
       <c r="N27" s="13">
         <v>1</v>
       </c>
@@ -3326,7 +3328,7 @@
         <v>10</v>
       </c>
       <c r="M31" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31" s="13">
         <v>2</v>
@@ -4914,7 +4916,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N8:Q62 N7 N2:Q6">
+  <conditionalFormatting sqref="N2:Q6 N7 N8:Q62">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5D48F-C4A0-0147-ACFE-2E88B31A7036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C00AF6-4A4E-814F-B7A3-02C9AB5DAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2240,10 +2240,10 @@
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P7" s="13">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" s="13">
         <v>1</v>
@@ -3112,10 +3112,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="13">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="O26" s="13">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="P26" s="13">
         <v>1</v>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C00AF6-4A4E-814F-B7A3-02C9AB5DAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D52EE6C-542C-7945-8ED4-A65D446392FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40660" yWindow="-7160" windowWidth="30540" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="418">
   <si>
     <t>subsector</t>
   </si>
@@ -1329,6 +1329,15 @@
   </si>
   <si>
     <t>strategy_5</t>
+  </si>
+  <si>
+    <t>TX:ENFU:ADJ_PRICES</t>
+  </si>
+  <si>
+    <t>Increase OR Decrease prices of fuels</t>
+  </si>
+  <si>
+    <t>transformation_enfu_adj_prices.yaml</t>
   </si>
 </sst>
 </file>
@@ -4792,24 +4801,44 @@
       </c>
       <c r="R63" s="42"/>
     </row>
-    <row r="64" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="16"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="25"/>
-      <c r="P64" s="25"/>
-      <c r="Q64" s="25"/>
+    <row r="64" spans="1:18" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="D64" s="36"/>
+      <c r="E64" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="K64" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="L64" s="10">
+        <v>10</v>
+      </c>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="13"/>
+      <c r="Q64" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
@@ -4880,7 +4909,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M64:M1048576 M1:M7 M47:M62 M9:M12 M14 M63:Q63 M16:M45">
+  <conditionalFormatting sqref="M65:M1048576 M1:M7 M47:M62 M9:M12 M14 M16:M45 M63:Q64">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
@@ -4892,7 +4921,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N64:N1048576">
+  <conditionalFormatting sqref="N65:N1048576">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="min"/>
@@ -4928,7 +4957,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O64:O1048576">
+  <conditionalFormatting sqref="O65:O1048576">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -4940,7 +4969,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P64:P1048576">
+  <conditionalFormatting sqref="P65:P1048576">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -4964,7 +4993,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q64:Q1048576">
+  <conditionalFormatting sqref="Q65:Q1048576">
     <cfRule type="colorScale" priority="53">
       <colorScale>
         <cfvo type="min"/>
@@ -4985,7 +5014,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" style="3" bestFit="1" customWidth="1"/>
@@ -5876,6 +5905,20 @@
         <v>409</v>
       </c>
     </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
